--- a/outputs/daily/hr_rankings_2026-07-31_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-31_remaining.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28988,7 +28988,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -36594,7 +36594,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
